--- a/tests/testdata/excel/ファイル名/v1.2.3.xlsx
+++ b/tests/testdata/excel/ファイル名/v1.2.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F1517C9-8471-4864-9620-3F49A9A0F69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{901C8D9E-3313-48FB-B502-ABBDC4082DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{D9EE8C5C-8BC9-4A0B-9F06-B740658BB095}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{49A7B612-A7A4-4450-ABEE-607297E4585C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47B6ECEA-A028-4708-8892-FC70D46334B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31572324-6B9F-4BD8-8C4A-669DA03E961E}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/v1.2.3.xlsx
+++ b/tests/testdata/excel/ファイル名/v1.2.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{901C8D9E-3313-48FB-B502-ABBDC4082DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25773E1D-2463-446C-B1BB-D3E88BBCFCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{49A7B612-A7A4-4450-ABEE-607297E4585C}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{02E7CEC5-6CA4-4C0A-9E1D-37D1E2D3DDC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31572324-6B9F-4BD8-8C4A-669DA03E961E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF4C86F3-D340-49A7-878E-A34C0CF7D2F6}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
